--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2506,6 +2506,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2515,7 +2518,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2677,6 +2680,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>108000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>110000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2719,7 +2725,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2881,6 +2887,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2890,7 +2899,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3052,6 +3061,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>145128.58746697762</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>150477.71562624906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3094,7 +3106,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3256,6 +3268,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3265,7 +3280,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3427,6 +3442,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>37128.587466977624</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>40477.715626249061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3448,11 +3466,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="469371136"/>
-        <c:axId val="469382656"/>
+        <c:axId val="447632896"/>
+        <c:axId val="522732672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="469371136"/>
+        <c:axId val="447632896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3495,14 +3513,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469382656"/>
+        <c:crossAx val="522732672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="469382656"/>
+        <c:axId val="522732672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3553,7 +3571,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469371136"/>
+        <c:crossAx val="447632896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3722,7 +3740,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3884,6 +3902,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3893,7 +3914,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4054,6 +4075,9 @@
                   <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>24000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4097,7 +4121,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4259,6 +4283,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4268,7 +4295,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4430,6 +4457,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>34096.741890604411</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>34883.591403841878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4472,7 +4502,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4634,6 +4664,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4643,7 +4676,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4805,6 +4838,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>10096.741890604411</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>10883.591403841878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4826,11 +4862,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475069824"/>
-        <c:axId val="475261952"/>
+        <c:axId val="559891584"/>
+        <c:axId val="590450688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475069824"/>
+        <c:axId val="559891584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4873,14 +4909,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475261952"/>
+        <c:crossAx val="590450688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475261952"/>
+        <c:axId val="590450688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4931,7 +4967,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475069824"/>
+        <c:crossAx val="559891584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5100,7 +5136,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5262,6 +5298,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5271,7 +5310,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5433,6 +5472,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>117000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>119000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5475,7 +5517,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5637,6 +5679,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5646,7 +5691,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5808,6 +5853,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>156673.21389222765</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>162288.75705714276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5850,7 +5898,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6012,6 +6060,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6021,7 +6072,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6183,6 +6234,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>39673.21389222765</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>43288.757057142764</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6204,11 +6258,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="535827968"/>
-        <c:axId val="535829504"/>
+        <c:axId val="701774848"/>
+        <c:axId val="595800832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="535827968"/>
+        <c:axId val="701774848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6251,14 +6305,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535829504"/>
+        <c:crossAx val="595800832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535829504"/>
+        <c:axId val="595800832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6309,7 +6363,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535827968"/>
+        <c:crossAx val="701774848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6478,7 +6532,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6640,6 +6694,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6649,7 +6706,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6811,6 +6868,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>112000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6853,7 +6913,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7015,6 +7075,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7024,7 +7087,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7186,6 +7249,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>148295.55114779418</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>153717.76323510444</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7228,7 +7294,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7390,6 +7456,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7399,7 +7468,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7561,6 +7630,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>38295.551147794176</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>41717.763235104445</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7582,11 +7654,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="577704320"/>
-        <c:axId val="577705856"/>
+        <c:axId val="595841408"/>
+        <c:axId val="595842944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="577704320"/>
+        <c:axId val="595841408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7629,14 +7701,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577705856"/>
+        <c:crossAx val="595842944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="577705856"/>
+        <c:axId val="595842944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7687,7 +7759,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="577704320"/>
+        <c:crossAx val="595841408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7856,7 +7928,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8018,6 +8090,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8027,7 +8102,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8189,6 +8264,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>108000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>110000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8231,7 +8309,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8393,6 +8471,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8402,7 +8483,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8564,6 +8645,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>145128.58746697762</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>150477.71562624906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8606,7 +8690,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8768,6 +8852,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8777,7 +8864,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8939,6 +9026,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>37128.587466977624</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>40477.715626249061</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8960,11 +9050,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="589760000"/>
-        <c:axId val="589761536"/>
+        <c:axId val="522577408"/>
+        <c:axId val="522578944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="589760000"/>
+        <c:axId val="522577408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9007,14 +9097,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="589761536"/>
+        <c:crossAx val="522578944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="589761536"/>
+        <c:axId val="522578944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9065,7 +9155,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="589760000"/>
+        <c:crossAx val="522577408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9619,7 +9709,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11508,6 +11598,35 @@
         <v>37128.587466977624</v>
       </c>
     </row>
+    <row r="57" spans="1:9" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="E57" s="18">
+        <v>141426.4230663786</v>
+      </c>
+      <c r="F57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="G57" s="18">
+        <v>110000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="I57" s="18">
+        <v>40477.715626249061</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11519,7 +11638,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13556,6 +13675,38 @@
         <v>-25.623704638394841</v>
       </c>
     </row>
+    <row r="57" spans="1:10" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>0</v>
+      </c>
+      <c r="D57" s="18">
+        <v>0</v>
+      </c>
+      <c r="E57" s="18">
+        <v>32785.329943524514</v>
+      </c>
+      <c r="F57" s="18">
+        <v>34883.591403841878</v>
+      </c>
+      <c r="G57" s="18">
+        <v>24000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>34883.591403841878</v>
+      </c>
+      <c r="I57" s="18">
+        <v>10883.591403841878</v>
+      </c>
+      <c r="J57" s="6">
+        <v>38.003913332402767</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13567,7 +13718,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16250,6 +16401,50 @@
         <v>75.343075358499476</v>
       </c>
     </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="E57" s="18">
+        <v>152527.02580551748</v>
+      </c>
+      <c r="F57" s="18">
+        <v>162288.75705714276</v>
+      </c>
+      <c r="G57" s="18">
+        <v>119000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>162288.75705714276</v>
+      </c>
+      <c r="I57" s="18">
+        <v>43288.757057142764</v>
+      </c>
+      <c r="J57" s="6">
+        <v>2.4000048637390137E-2</v>
+      </c>
+      <c r="K57" s="6">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="L57" s="6">
+        <v>2.4000048637390137E-2</v>
+      </c>
+      <c r="M57" s="6">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="N57" s="1">
+        <v>77.665854024250493</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16261,7 +16456,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -19453,6 +19648,59 @@
         <v>83.790672900129579</v>
       </c>
     </row>
+    <row r="57" spans="1:17" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="E57" s="18">
+        <v>144471.58056347485</v>
+      </c>
+      <c r="F57" s="18">
+        <v>153717.76323510444</v>
+      </c>
+      <c r="G57" s="18">
+        <v>112000</v>
+      </c>
+      <c r="H57" s="18">
+        <v>153717.76323510444</v>
+      </c>
+      <c r="I57" s="18">
+        <v>41717.763235104445</v>
+      </c>
+      <c r="J57" s="6">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="K57" s="6">
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="L57" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M57" s="6">
+        <v>0.6589999794960022</v>
+      </c>
+      <c r="N57" s="6">
+        <v>82.317072210415034</v>
+      </c>
+      <c r="O57" s="6">
+        <v>82.130142596708495</v>
+      </c>
+      <c r="P57" s="6">
+        <v>81.483167688714857</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>83.424092412695785</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19464,7 +19712,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21518,6 +21766,38 @@
         <v>37128.587466977624</v>
       </c>
     </row>
+    <row r="57" spans="1:10" ht="12.75">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="18">
+        <v>1879.6992295875662</v>
+      </c>
+      <c r="F57" s="18">
+        <v>141426.4230663786</v>
+      </c>
+      <c r="G57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="H57" s="18">
+        <v>110000</v>
+      </c>
+      <c r="I57" s="18">
+        <v>150477.71562624906</v>
+      </c>
+      <c r="J57" s="18">
+        <v>40477.715626249061</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2509,6 +2509,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2518,7 +2521,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2683,6 +2686,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>112000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2725,7 +2731,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2890,6 +2896,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2899,7 +2908,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3064,6 +3073,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>150477.71562624906</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>153609.12930365079</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3106,7 +3118,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3271,6 +3283,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3280,7 +3295,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3445,6 +3460,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>40477.715626249061</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>41609.129303650785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3466,11 +3484,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="447632896"/>
-        <c:axId val="522732672"/>
+        <c:axId val="557293952"/>
+        <c:axId val="557295488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="447632896"/>
+        <c:axId val="557293952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3513,14 +3531,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522732672"/>
+        <c:crossAx val="557295488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522732672"/>
+        <c:axId val="557295488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3571,7 +3589,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447632896"/>
+        <c:crossAx val="557293952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3740,7 +3758,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3905,6 +3923,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3914,7 +3935,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4079,6 +4100,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>24000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4121,7 +4145,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4286,6 +4310,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4295,7 +4322,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4460,6 +4487,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>34883.591403841878</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>37145.874574921043</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4502,7 +4532,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4667,6 +4697,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4676,7 +4709,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4841,6 +4874,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>10883.591403841878</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>11145.874574921043</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4862,11 +4898,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559891584"/>
-        <c:axId val="590450688"/>
+        <c:axId val="615683200"/>
+        <c:axId val="615685120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559891584"/>
+        <c:axId val="615683200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4909,14 +4945,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590450688"/>
+        <c:crossAx val="615685120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="590450688"/>
+        <c:axId val="615685120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4967,7 +5003,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559891584"/>
+        <c:crossAx val="615683200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5136,7 +5172,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5301,6 +5337,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5310,7 +5349,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5475,6 +5514,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>119000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>121000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5517,7 +5559,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5682,6 +5724,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5691,7 +5736,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5856,6 +5901,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>162288.75705714276</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>165508.97573642572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5898,7 +5946,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6063,6 +6111,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6072,7 +6123,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6237,6 +6288,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>43288.757057142764</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>44508.975736425724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6258,11 +6312,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="701774848"/>
-        <c:axId val="595800832"/>
+        <c:axId val="639818752"/>
+        <c:axId val="639820544"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="701774848"/>
+        <c:axId val="639818752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6305,14 +6359,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595800832"/>
+        <c:crossAx val="639820544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="595800832"/>
+        <c:axId val="639820544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6363,7 +6417,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="701774848"/>
+        <c:crossAx val="639818752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6532,7 +6586,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6697,6 +6751,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6706,7 +6763,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6871,6 +6928,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>114000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6913,7 +6973,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7078,6 +7138,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7087,7 +7150,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7252,6 +7315,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>153717.76323510444</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>156873.53822185245</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7294,7 +7360,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7459,6 +7525,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7468,7 +7537,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7633,6 +7702,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>41717.763235104445</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>42873.538221852446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7654,11 +7726,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="595841408"/>
-        <c:axId val="595842944"/>
+        <c:axId val="640864640"/>
+        <c:axId val="640866176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="595841408"/>
+        <c:axId val="640864640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7701,14 +7773,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595842944"/>
+        <c:crossAx val="640866176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="595842944"/>
+        <c:axId val="640866176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7759,7 +7831,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595841408"/>
+        <c:crossAx val="640864640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7928,7 +8000,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8093,6 +8165,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8102,7 +8177,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8267,6 +8342,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>112000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8309,7 +8387,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8474,6 +8552,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8483,7 +8564,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8648,6 +8729,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>150477.71562624906</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>153609.12930365079</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8690,7 +8774,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8855,6 +8939,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8864,7 +8951,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9029,6 +9116,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>40477.715626249061</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>41609.129303650785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9050,11 +9140,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522577408"/>
-        <c:axId val="522578944"/>
+        <c:axId val="642140032"/>
+        <c:axId val="642141568"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522577408"/>
+        <c:axId val="642140032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9097,14 +9187,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522578944"/>
+        <c:crossAx val="642141568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522578944"/>
+        <c:axId val="642141568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9155,7 +9245,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522577408"/>
+        <c:crossAx val="642140032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9709,7 +9799,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11627,6 +11717,35 @@
         <v>40477.715626249061</v>
       </c>
     </row>
+    <row r="58" spans="1:9" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>143292.09466169687</v>
+      </c>
+      <c r="F58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="G58" s="18">
+        <v>112000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="I58" s="18">
+        <v>41609.129303650785</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11638,7 +11757,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13707,6 +13826,38 @@
         <v>38.003913332402767</v>
       </c>
     </row>
+    <row r="58" spans="1:10" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F58" s="18">
+        <v>37145.874574921043</v>
+      </c>
+      <c r="G58" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>37145.874574921043</v>
+      </c>
+      <c r="I58" s="18">
+        <v>11145.874574921043</v>
+      </c>
+      <c r="J58" s="6">
+        <v>-130.04693515337254</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13718,7 +13869,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16445,6 +16596,50 @@
         <v>77.665854024250493</v>
       </c>
     </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>154392.69740083575</v>
+      </c>
+      <c r="F58" s="18">
+        <v>165508.97573642572</v>
+      </c>
+      <c r="G58" s="18">
+        <v>121000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>165508.97573642572</v>
+      </c>
+      <c r="I58" s="18">
+        <v>44508.975736425724</v>
+      </c>
+      <c r="J58" s="6">
+        <v>8.0000162124633789E-3</v>
+      </c>
+      <c r="K58" s="6">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="L58" s="6">
+        <v>8.0000162124633789E-3</v>
+      </c>
+      <c r="M58" s="6">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="N58" s="1">
+        <v>78.476878875019352</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16456,7 +16651,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -19701,6 +19896,59 @@
         <v>83.424092412695785</v>
       </c>
     </row>
+    <row r="58" spans="1:17" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="E58" s="18">
+        <v>146337.25215879313</v>
+      </c>
+      <c r="F58" s="18">
+        <v>156873.53822185245</v>
+      </c>
+      <c r="G58" s="18">
+        <v>114000</v>
+      </c>
+      <c r="H58" s="18">
+        <v>156873.53822185245</v>
+      </c>
+      <c r="I58" s="18">
+        <v>42873.538221852446</v>
+      </c>
+      <c r="J58" s="6">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="K58" s="6">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="L58" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M58" s="6">
+        <v>0.7720000147819519</v>
+      </c>
+      <c r="N58" s="6">
+        <v>79.155674275563754</v>
+      </c>
+      <c r="O58" s="6">
+        <v>81.138653156326924</v>
+      </c>
+      <c r="P58" s="6">
+        <v>81.368329511252213</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>80.679300446476333</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19712,7 +19960,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21798,6 +22046,38 @@
         <v>40477.715626249061</v>
       </c>
     </row>
+    <row r="58" spans="1:10" ht="12.75">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="18">
+        <v>1865.6715953182777</v>
+      </c>
+      <c r="F58" s="18">
+        <v>143292.09466169687</v>
+      </c>
+      <c r="G58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="H58" s="18">
+        <v>112000</v>
+      </c>
+      <c r="I58" s="18">
+        <v>153609.12930365079</v>
+      </c>
+      <c r="J58" s="18">
+        <v>41609.129303650785</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2512,6 +2512,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2521,7 +2524,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2689,6 +2692,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>114000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2731,7 +2737,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2899,6 +2905,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2908,7 +2917,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3076,6 +3085,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>153609.12930365079</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>156039.00859402367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3118,7 +3130,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3286,6 +3298,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3295,7 +3310,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3463,6 +3478,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>41609.129303650785</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>42039.008594023675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3484,11 +3502,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557293952"/>
-        <c:axId val="557295488"/>
+        <c:axId val="396994432"/>
+        <c:axId val="397587200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557293952"/>
+        <c:axId val="396994432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3531,14 +3549,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557295488"/>
+        <c:crossAx val="397587200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557295488"/>
+        <c:axId val="397587200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3589,7 +3607,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557293952"/>
+        <c:crossAx val="396994432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3758,7 +3776,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3926,6 +3944,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3935,7 +3956,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4102,6 +4123,9 @@
                   <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4145,7 +4169,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4313,6 +4337,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4322,7 +4349,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4490,6 +4517,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>37145.874574921043</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>37249.828306544514</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4532,7 +4562,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4700,6 +4730,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4709,7 +4742,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4877,6 +4910,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>11145.874574921043</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>11249.828306544514</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4898,11 +4934,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="615683200"/>
-        <c:axId val="615685120"/>
+        <c:axId val="483330304"/>
+        <c:axId val="483410304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="615683200"/>
+        <c:axId val="483330304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4945,14 +4981,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615685120"/>
+        <c:crossAx val="483410304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="615685120"/>
+        <c:axId val="483410304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5003,7 +5039,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615683200"/>
+        <c:crossAx val="483330304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5172,7 +5208,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5340,6 +5376,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5349,7 +5388,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5517,6 +5556,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>121000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>123000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5559,7 +5601,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5727,6 +5769,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5736,7 +5781,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5904,6 +5949,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>165508.97573642572</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>167972.15706791595</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5946,7 +5994,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6114,6 +6162,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6123,7 +6174,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6291,6 +6342,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>44508.975736425724</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>44972.157067915949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6312,11 +6366,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="639818752"/>
-        <c:axId val="639820544"/>
+        <c:axId val="623973504"/>
+        <c:axId val="623975040"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="639818752"/>
+        <c:axId val="623973504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6359,14 +6413,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="639820544"/>
+        <c:crossAx val="623975040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="639820544"/>
+        <c:axId val="623975040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6417,7 +6471,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="639818752"/>
+        <c:crossAx val="623973504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6586,7 +6640,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6754,6 +6808,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6763,7 +6820,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6931,6 +6988,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>116000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6973,7 +7033,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7141,6 +7201,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7150,7 +7213,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7318,6 +7381,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>156873.53822185245</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>159312.55304860655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7360,7 +7426,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7528,6 +7594,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7537,7 +7606,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7705,6 +7774,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>42873.538221852446</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>43312.553048606555</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7726,11 +7798,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="640864640"/>
-        <c:axId val="640866176"/>
+        <c:axId val="528292480"/>
+        <c:axId val="528302464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="640864640"/>
+        <c:axId val="528292480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7773,14 +7845,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="640866176"/>
+        <c:crossAx val="528302464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="640866176"/>
+        <c:axId val="528302464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7831,7 +7903,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="640864640"/>
+        <c:crossAx val="528292480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8000,7 +8072,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8168,6 +8240,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8177,7 +8252,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8345,6 +8420,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>112000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>114000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8387,7 +8465,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8555,6 +8633,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8564,7 +8645,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8732,6 +8813,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>153609.12930365079</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>156039.00859402367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8774,7 +8858,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8942,6 +9026,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8951,7 +9038,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9119,6 +9206,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>41609.129303650785</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>42039.008594023675</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9140,11 +9230,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="642140032"/>
-        <c:axId val="642141568"/>
+        <c:axId val="528322944"/>
+        <c:axId val="528324480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="642140032"/>
+        <c:axId val="528322944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9187,14 +9277,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="642141568"/>
+        <c:crossAx val="528324480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="642141568"/>
+        <c:axId val="528324480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9245,7 +9335,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="642140032"/>
+        <c:crossAx val="528322944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9799,7 +9889,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11746,6 +11836,35 @@
         <v>41609.129303650785</v>
       </c>
     </row>
+    <row r="59" spans="1:9" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="E59" s="18">
+        <v>145152.5596954514</v>
+      </c>
+      <c r="F59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="G59" s="18">
+        <v>114000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="I59" s="18">
+        <v>42039.008594023675</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11757,7 +11876,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -13858,6 +13977,38 @@
         <v>-130.04693515337254</v>
       </c>
     </row>
+    <row r="59" spans="1:10" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>0</v>
+      </c>
+      <c r="D59" s="18">
+        <v>0</v>
+      </c>
+      <c r="E59" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F59" s="18">
+        <v>37249.828306544514</v>
+      </c>
+      <c r="G59" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>37249.828306544514</v>
+      </c>
+      <c r="I59" s="18">
+        <v>11249.828306544514</v>
+      </c>
+      <c r="J59" s="6">
+        <v>38.965935849742465</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13869,7 +14020,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16640,6 +16791,50 @@
         <v>78.476878875019352</v>
       </c>
     </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="E59" s="18">
+        <v>156253.16243459028</v>
+      </c>
+      <c r="F59" s="18">
+        <v>167972.15706791595</v>
+      </c>
+      <c r="G59" s="18">
+        <v>123000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>167972.15706791595</v>
+      </c>
+      <c r="I59" s="18">
+        <v>44972.157067915949</v>
+      </c>
+      <c r="J59" s="6">
+        <v>3.0000209808349609E-3</v>
+      </c>
+      <c r="K59" s="6">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="L59" s="6">
+        <v>3.0000209808349609E-3</v>
+      </c>
+      <c r="M59" s="6">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="N59" s="1">
+        <v>78.82293398981966</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16651,7 +16846,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -19949,6 +20144,59 @@
         <v>80.679300446476333</v>
       </c>
     </row>
+    <row r="59" spans="1:17" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="E59" s="18">
+        <v>148197.71719254766</v>
+      </c>
+      <c r="F59" s="18">
+        <v>159312.55304860655</v>
+      </c>
+      <c r="G59" s="18">
+        <v>116000</v>
+      </c>
+      <c r="H59" s="18">
+        <v>159312.55304860655</v>
+      </c>
+      <c r="I59" s="18">
+        <v>43312.553048606555</v>
+      </c>
+      <c r="J59" s="6">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="K59" s="6">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="L59" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M59" s="6">
+        <v>0.7720000147819519</v>
+      </c>
+      <c r="N59" s="6">
+        <v>79.947236522705992</v>
+      </c>
+      <c r="O59" s="6">
+        <v>80.74151427845328</v>
+      </c>
+      <c r="P59" s="6">
+        <v>81.15939110031924</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>79.905760634721361</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19960,7 +20208,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -22078,6 +22326,38 @@
         <v>41609.129303650785</v>
       </c>
     </row>
+    <row r="59" spans="1:10" ht="12.75">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="18">
+        <v>1860.4650337545247</v>
+      </c>
+      <c r="F59" s="18">
+        <v>145152.5596954514</v>
+      </c>
+      <c r="G59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="H59" s="18">
+        <v>114000</v>
+      </c>
+      <c r="I59" s="18">
+        <v>156039.00859402367</v>
+      </c>
+      <c r="J59" s="18">
+        <v>42039.008594023675</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2515,6 +2515,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2524,7 +2527,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2695,6 +2698,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>116000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2737,7 +2743,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2908,6 +2914,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2917,7 +2926,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3088,6 +3097,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>156039.00859402367</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>154119.87937698292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3130,7 +3142,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3301,6 +3313,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3310,7 +3325,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3481,6 +3496,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>42039.008594023675</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>38119.879376982921</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3502,11 +3520,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="396994432"/>
-        <c:axId val="397587200"/>
+        <c:axId val="393925376"/>
+        <c:axId val="395000064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="396994432"/>
+        <c:axId val="393925376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3549,14 +3567,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397587200"/>
+        <c:crossAx val="395000064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="397587200"/>
+        <c:axId val="395000064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3607,7 +3625,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="396994432"/>
+        <c:crossAx val="393925376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3776,7 +3794,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3947,6 +3965,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3956,7 +3977,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4126,6 +4147,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4169,7 +4193,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4340,6 +4364,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4349,7 +4376,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4520,6 +4547,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>37249.828306544514</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>36314.248852654535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4562,7 +4592,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4733,6 +4763,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4742,7 +4775,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4913,6 +4946,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>11249.828306544514</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>10314.248852654535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4934,11 +4970,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483330304"/>
-        <c:axId val="483410304"/>
+        <c:axId val="427815296"/>
+        <c:axId val="427817984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483330304"/>
+        <c:axId val="427815296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4981,14 +5017,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483410304"/>
+        <c:crossAx val="427817984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483410304"/>
+        <c:axId val="427817984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5039,7 +5075,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483330304"/>
+        <c:crossAx val="427815296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5208,7 +5244,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5379,6 +5415,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5388,7 +5427,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5559,6 +5598,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>123000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>125000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5601,7 +5643,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5772,6 +5814,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5781,7 +5826,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5952,6 +5997,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>167972.15706791595</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>165753.31080411418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5994,7 +6042,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6165,6 +6213,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6174,7 +6225,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6345,6 +6396,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>44972.157067915949</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>40753.310804114182</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6366,11 +6420,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="623973504"/>
-        <c:axId val="623975040"/>
+        <c:axId val="79826304"/>
+        <c:axId val="79828096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="623973504"/>
+        <c:axId val="79826304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6413,14 +6467,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623975040"/>
+        <c:crossAx val="79828096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623975040"/>
+        <c:axId val="79828096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6471,7 +6525,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623973504"/>
+        <c:crossAx val="79826304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6640,7 +6694,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6811,6 +6865,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6820,7 +6877,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6991,6 +7048,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>116000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>118000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7033,7 +7093,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7204,6 +7264,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7213,7 +7276,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7384,6 +7447,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>159312.55304860655</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>157311.20436714575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7426,7 +7492,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7597,6 +7663,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7606,7 +7675,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7777,6 +7846,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>43312.553048606555</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>39311.20436714575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7798,11 +7870,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528292480"/>
-        <c:axId val="528302464"/>
+        <c:axId val="79856384"/>
+        <c:axId val="79857920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528292480"/>
+        <c:axId val="79856384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7845,14 +7917,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528302464"/>
+        <c:crossAx val="79857920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528302464"/>
+        <c:axId val="79857920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7903,7 +7975,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528292480"/>
+        <c:crossAx val="79856384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8072,7 +8144,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8243,6 +8315,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8252,7 +8327,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8423,6 +8498,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>114000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>116000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8465,7 +8543,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8636,6 +8714,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8645,7 +8726,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8816,6 +8897,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>156039.00859402367</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>154119.87937698292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8858,7 +8942,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9029,6 +9113,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9038,7 +9125,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9209,6 +9296,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>42039.008594023675</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>38119.879376982921</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9230,11 +9320,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528322944"/>
-        <c:axId val="528324480"/>
+        <c:axId val="80058240"/>
+        <c:axId val="80059776"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528322944"/>
+        <c:axId val="80058240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9277,14 +9367,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528324480"/>
+        <c:crossAx val="80059776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528324480"/>
+        <c:axId val="80059776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9335,7 +9425,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528322944"/>
+        <c:crossAx val="80058240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9889,7 +9979,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11865,6 +11955,35 @@
         <v>42039.008594023675</v>
       </c>
     </row>
+    <row r="60" spans="1:9" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="E60" s="18">
+        <v>147060.95668195881</v>
+      </c>
+      <c r="F60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="G60" s="18">
+        <v>116000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="I60" s="18">
+        <v>38119.879376982921</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11876,7 +11995,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14009,6 +14128,38 @@
         <v>38.965935849742465</v>
       </c>
     </row>
+    <row r="60" spans="1:10" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>0</v>
+      </c>
+      <c r="D60" s="18">
+        <v>0</v>
+      </c>
+      <c r="E60" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F60" s="18">
+        <v>36314.248852654535</v>
+      </c>
+      <c r="G60" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>36314.248852654535</v>
+      </c>
+      <c r="I60" s="18">
+        <v>10314.248852654535</v>
+      </c>
+      <c r="J60" s="6">
+        <v>-89.784897005371036</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14020,7 +14171,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16835,6 +16986,50 @@
         <v>78.82293398981966</v>
       </c>
     </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="E60" s="18">
+        <v>158161.55942109769</v>
+      </c>
+      <c r="F60" s="18">
+        <v>165753.31080411418</v>
+      </c>
+      <c r="G60" s="18">
+        <v>125000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>165753.31080411418</v>
+      </c>
+      <c r="I60" s="18">
+        <v>40753.310804114182</v>
+      </c>
+      <c r="J60" s="6">
+        <v>0</v>
+      </c>
+      <c r="K60" s="6">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="L60" s="6">
+        <v>2.7000069618225098E-2</v>
+      </c>
+      <c r="M60" s="6">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="N60" s="1">
+        <v>67.160806984825626</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16846,7 +17041,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20197,6 +20392,59 @@
         <v>79.905760634721361</v>
       </c>
     </row>
+    <row r="60" spans="1:17" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="E60" s="18">
+        <v>150106.11417905506</v>
+      </c>
+      <c r="F60" s="18">
+        <v>157311.20436714575</v>
+      </c>
+      <c r="G60" s="18">
+        <v>118000</v>
+      </c>
+      <c r="H60" s="18">
+        <v>157311.20436714575</v>
+      </c>
+      <c r="I60" s="18">
+        <v>39311.20436714575</v>
+      </c>
+      <c r="J60" s="6">
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="K60" s="6">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="L60" s="6">
+        <v>1.1510000228881836</v>
+      </c>
+      <c r="M60" s="6">
+        <v>0.80000001192092896</v>
+      </c>
+      <c r="N60" s="6">
+        <v>70.655258802170835</v>
+      </c>
+      <c r="O60" s="6">
+        <v>77.37942911969246</v>
+      </c>
+      <c r="P60" s="6">
+        <v>79.899403773443638</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>72.339479812190092</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20208,7 +20456,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -22358,6 +22606,38 @@
         <v>42039.008594023675</v>
       </c>
     </row>
+    <row r="60" spans="1:10" ht="12.75">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="18">
+        <v>1908.3969865073964</v>
+      </c>
+      <c r="F60" s="18">
+        <v>147060.95668195881</v>
+      </c>
+      <c r="G60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="H60" s="18">
+        <v>116000</v>
+      </c>
+      <c r="I60" s="18">
+        <v>154119.87937698292</v>
+      </c>
+      <c r="J60" s="18">
+        <v>38119.879376982921</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2518,6 +2518,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2527,7 +2530,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2701,6 +2704,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>116000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>118000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2743,7 +2749,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2917,6 +2923,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2926,7 +2935,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3100,6 +3109,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>154119.87937698292</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>175090.75274658189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3142,7 +3154,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3316,6 +3328,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3325,7 +3340,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3499,6 +3514,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>38119.879376982921</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>57090.752746581886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3520,11 +3538,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="393925376"/>
-        <c:axId val="395000064"/>
+        <c:axId val="463891072"/>
+        <c:axId val="472212224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="393925376"/>
+        <c:axId val="463891072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3567,14 +3585,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395000064"/>
+        <c:crossAx val="472212224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395000064"/>
+        <c:axId val="472212224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3625,7 +3643,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393925376"/>
+        <c:crossAx val="463891072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3794,7 +3812,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3968,6 +3986,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3977,7 +3998,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4150,6 +4171,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4193,7 +4217,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4367,6 +4391,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4376,7 +4403,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4550,6 +4577,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>36314.248852654535</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>40784.23039741494</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4592,7 +4622,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4766,6 +4796,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4775,7 +4808,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4949,6 +4982,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>10314.248852654535</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>14784.23039741494</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4970,11 +5006,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="427815296"/>
-        <c:axId val="427817984"/>
+        <c:axId val="544982528"/>
+        <c:axId val="544984064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="427815296"/>
+        <c:axId val="544982528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5017,14 +5053,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427817984"/>
+        <c:crossAx val="544984064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="427817984"/>
+        <c:axId val="544984064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5075,7 +5111,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427815296"/>
+        <c:crossAx val="544982528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5244,7 +5280,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5418,6 +5454,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5427,7 +5466,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5601,6 +5640,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>125000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>127000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5643,7 +5685,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5817,6 +5859,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5826,7 +5871,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6000,6 +6045,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>165753.31080411418</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>188156.1626786936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6042,7 +6090,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6216,6 +6264,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6225,7 +6276,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6399,6 +6450,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>40753.310804114182</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>61156.162678693596</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6420,11 +6474,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79826304"/>
-        <c:axId val="79828096"/>
+        <c:axId val="545045120"/>
+        <c:axId val="545046912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79826304"/>
+        <c:axId val="545045120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6467,14 +6521,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79828096"/>
+        <c:crossAx val="545046912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79828096"/>
+        <c:axId val="545046912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6525,7 +6579,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79826304"/>
+        <c:crossAx val="545045120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6694,7 +6748,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6868,6 +6922,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6877,7 +6934,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7051,6 +7108,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>118000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>120000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7093,7 +7153,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7267,6 +7327,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7276,7 +7339,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7450,6 +7513,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>157311.20436714575</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>178674.90326006041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7492,7 +7558,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7666,6 +7732,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7675,7 +7744,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7849,6 +7918,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>39311.20436714575</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>58674.903260060411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7870,11 +7942,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79856384"/>
-        <c:axId val="79857920"/>
+        <c:axId val="545144832"/>
+        <c:axId val="545146368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79856384"/>
+        <c:axId val="545144832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7917,14 +7989,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79857920"/>
+        <c:crossAx val="545146368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79857920"/>
+        <c:axId val="545146368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7975,7 +8047,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79856384"/>
+        <c:crossAx val="545144832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8144,7 +8216,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8318,6 +8390,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8327,7 +8402,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8501,6 +8576,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>116000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>118000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8543,7 +8621,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8717,6 +8795,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8726,7 +8807,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8900,6 +8981,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>154119.87937698292</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>175090.75274658189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8942,7 +9026,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9116,6 +9200,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9125,7 +9212,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9299,6 +9386,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>38119.879376982921</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>57090.752746581886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9320,11 +9410,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80058240"/>
-        <c:axId val="80059776"/>
+        <c:axId val="545789056"/>
+        <c:axId val="545790592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80058240"/>
+        <c:axId val="545789056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9367,14 +9457,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80059776"/>
+        <c:crossAx val="545790592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80059776"/>
+        <c:axId val="545790592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9425,7 +9515,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80058240"/>
+        <c:crossAx val="545789056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9979,7 +10069,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -11984,6 +12074,35 @@
         <v>38119.879376982921</v>
       </c>
     </row>
+    <row r="61" spans="1:9" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="E61" s="18">
+        <v>148760.19195996661</v>
+      </c>
+      <c r="F61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="G61" s="18">
+        <v>118000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="I61" s="18">
+        <v>57090.752746581886</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11995,7 +12114,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14160,6 +14279,38 @@
         <v>-89.784897005371036</v>
       </c>
     </row>
+    <row r="61" spans="1:10" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>0</v>
+      </c>
+      <c r="D61" s="18">
+        <v>0</v>
+      </c>
+      <c r="E61" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F61" s="18">
+        <v>40784.23039741494</v>
+      </c>
+      <c r="G61" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>40784.23039741494</v>
+      </c>
+      <c r="I61" s="18">
+        <v>14784.23039741494</v>
+      </c>
+      <c r="J61" s="6">
+        <v>95.218135798121537</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14171,7 +14322,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17030,6 +17181,50 @@
         <v>67.160806984825626</v>
       </c>
     </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="E61" s="18">
+        <v>159860.79469910549</v>
+      </c>
+      <c r="F61" s="18">
+        <v>188156.1626786936</v>
+      </c>
+      <c r="G61" s="18">
+        <v>127000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>188156.1626786936</v>
+      </c>
+      <c r="I61" s="18">
+        <v>61156.162678693596</v>
+      </c>
+      <c r="J61" s="6">
+        <v>0.12900006771087646</v>
+      </c>
+      <c r="K61" s="6">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="L61" s="6">
+        <v>0.12900006771087646</v>
+      </c>
+      <c r="M61" s="6">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="N61" s="1">
+        <v>82.232420296691927</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17041,7 +17236,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20445,6 +20640,59 @@
         <v>72.339479812190092</v>
       </c>
     </row>
+    <row r="61" spans="1:17" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="E61" s="18">
+        <v>151805.34945706287</v>
+      </c>
+      <c r="F61" s="18">
+        <v>178674.90326006041</v>
+      </c>
+      <c r="G61" s="18">
+        <v>120000</v>
+      </c>
+      <c r="H61" s="18">
+        <v>178674.90326006041</v>
+      </c>
+      <c r="I61" s="18">
+        <v>58674.903260060411</v>
+      </c>
+      <c r="J61" s="6">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="L61" s="6">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="M61" s="6">
+        <v>0.8399999737739563</v>
+      </c>
+      <c r="N61" s="6">
+        <v>96.011413524955756</v>
+      </c>
+      <c r="O61" s="6">
+        <v>83.590090588113569</v>
+      </c>
+      <c r="P61" s="6">
+        <v>81.129632711666943</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>88.511006341006805</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20456,7 +20704,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -22638,6 +22886,38 @@
         <v>38119.879376982921</v>
       </c>
     </row>
+    <row r="61" spans="1:10" ht="12.75">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="18">
+        <v>1699.2352780078011</v>
+      </c>
+      <c r="F61" s="18">
+        <v>148760.19195996661</v>
+      </c>
+      <c r="G61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="H61" s="18">
+        <v>118000</v>
+      </c>
+      <c r="I61" s="18">
+        <v>175090.75274658189</v>
+      </c>
+      <c r="J61" s="18">
+        <v>57090.752746581886</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2521,6 +2521,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2530,7 +2533,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2707,6 +2710,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>118000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>120000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2749,7 +2755,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2926,6 +2932,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2935,7 +2944,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3112,6 +3121,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>175090.75274658189</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>187206.43969950231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3154,7 +3166,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3331,6 +3343,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3340,7 +3355,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3517,6 +3532,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>57090.752746581886</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>67206.439699502313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3538,11 +3556,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="463891072"/>
-        <c:axId val="472212224"/>
+        <c:axId val="161226752"/>
+        <c:axId val="161228288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="463891072"/>
+        <c:axId val="161226752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3585,14 +3603,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472212224"/>
+        <c:crossAx val="161228288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472212224"/>
+        <c:axId val="161228288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3643,7 +3661,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="463891072"/>
+        <c:crossAx val="161226752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3812,7 +3830,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3989,6 +4007,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3998,7 +4019,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4174,6 +4195,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4217,7 +4241,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4394,6 +4418,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4403,7 +4430,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4580,6 +4607,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>40784.23039741494</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>43140.497081088128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4622,7 +4652,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4799,6 +4829,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4808,7 +4841,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4985,6 +5018,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>14784.23039741494</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17140.497081088128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5006,11 +5042,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="544982528"/>
-        <c:axId val="544984064"/>
+        <c:axId val="426123264"/>
+        <c:axId val="426124800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="544982528"/>
+        <c:axId val="426123264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5053,14 +5089,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="544984064"/>
+        <c:crossAx val="426124800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="544984064"/>
+        <c:axId val="426124800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5111,7 +5147,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="544982528"/>
+        <c:crossAx val="426123264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5280,7 +5316,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5457,6 +5493,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5466,7 +5505,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5643,6 +5682,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>127000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>129000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5685,7 +5727,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5862,6 +5904,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5871,7 +5916,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6048,6 +6093,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>188156.1626786936</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>201026.69016266201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6090,7 +6138,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6267,6 +6315,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6276,7 +6327,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6453,6 +6504,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>61156.162678693596</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>72026.690162662009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6474,11 +6528,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="545045120"/>
-        <c:axId val="545046912"/>
+        <c:axId val="442375552"/>
+        <c:axId val="448738816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="545045120"/>
+        <c:axId val="442375552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6521,14 +6575,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="545046912"/>
+        <c:crossAx val="448738816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="545046912"/>
+        <c:axId val="448738816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6579,7 +6633,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="545045120"/>
+        <c:crossAx val="442375552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6748,7 +6802,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6925,6 +6979,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6934,7 +6991,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7111,6 +7168,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>122000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7153,7 +7213,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7330,6 +7390,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7339,7 +7402,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7516,6 +7579,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>178674.90326006041</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>190997.66079790759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7558,7 +7624,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7735,6 +7801,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7744,7 +7813,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7921,6 +7990,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>58674.903260060411</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>68997.660797907592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7942,11 +8014,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="545144832"/>
-        <c:axId val="545146368"/>
+        <c:axId val="524067584"/>
+        <c:axId val="524069120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="545144832"/>
+        <c:axId val="524067584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7989,14 +8061,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="545146368"/>
+        <c:crossAx val="524069120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="545146368"/>
+        <c:axId val="524069120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8047,7 +8119,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="545144832"/>
+        <c:crossAx val="524067584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8216,7 +8288,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8393,6 +8465,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8402,7 +8477,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8579,6 +8654,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>118000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>120000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8621,7 +8699,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8798,6 +8876,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8807,7 +8888,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8984,6 +9065,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>175090.75274658189</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>187206.43969950231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9026,7 +9110,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9203,6 +9287,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9212,7 +9299,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9389,6 +9476,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>57090.752746581886</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>67206.439699502313</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9410,11 +9500,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="545789056"/>
-        <c:axId val="545790592"/>
+        <c:axId val="472297472"/>
+        <c:axId val="472299008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="545789056"/>
+        <c:axId val="472297472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9457,14 +9547,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="545790592"/>
+        <c:crossAx val="472299008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="545790592"/>
+        <c:axId val="472299008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9515,7 +9605,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="545789056"/>
+        <c:crossAx val="472297472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10069,7 +10159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12103,6 +12193,35 @@
         <v>57090.752746581886</v>
       </c>
     </row>
+    <row r="62" spans="1:9" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="E62" s="18">
+        <v>150366.61765662523</v>
+      </c>
+      <c r="F62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="G62" s="18">
+        <v>120000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="I62" s="18">
+        <v>67206.439699502313</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12114,7 +12233,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14311,6 +14430,38 @@
         <v>95.218135798121537</v>
       </c>
     </row>
+    <row r="62" spans="1:10" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>0</v>
+      </c>
+      <c r="D62" s="18">
+        <v>0</v>
+      </c>
+      <c r="E62" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F62" s="18">
+        <v>43140.497081088128</v>
+      </c>
+      <c r="G62" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>43140.497081088128</v>
+      </c>
+      <c r="I62" s="18">
+        <v>17140.497081088128</v>
+      </c>
+      <c r="J62" s="6">
+        <v>107.7933992308817</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14322,7 +14473,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17225,6 +17376,50 @@
         <v>82.232420296691927</v>
       </c>
     </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="E62" s="18">
+        <v>161467.2203957641</v>
+      </c>
+      <c r="F62" s="18">
+        <v>201026.69016266201</v>
+      </c>
+      <c r="G62" s="18">
+        <v>129000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>201026.69016266201</v>
+      </c>
+      <c r="I62" s="18">
+        <v>72026.690162662009</v>
+      </c>
+      <c r="J62" s="6">
+        <v>6.7999958992004395E-2</v>
+      </c>
+      <c r="K62" s="6">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="L62" s="6">
+        <v>6.7999958992004395E-2</v>
+      </c>
+      <c r="M62" s="6">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="N62" s="1">
+        <v>86.230028778736084</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17236,7 +17431,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20693,6 +20888,59 @@
         <v>88.511006341006805</v>
       </c>
     </row>
+    <row r="62" spans="1:17" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="E62" s="18">
+        <v>153411.77515372148</v>
+      </c>
+      <c r="F62" s="18">
+        <v>190997.66079790759</v>
+      </c>
+      <c r="G62" s="18">
+        <v>122000</v>
+      </c>
+      <c r="H62" s="18">
+        <v>190997.66079790759</v>
+      </c>
+      <c r="I62" s="18">
+        <v>68997.660797907592</v>
+      </c>
+      <c r="J62" s="6">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="K62" s="6">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="L62" s="6">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="M62" s="6">
+        <v>0.88899999856948853</v>
+      </c>
+      <c r="N62" s="6">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="O62" s="6">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="P62" s="6">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>94.913940221952458</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20704,7 +20952,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -22918,6 +23166,38 @@
         <v>57090.752746581886</v>
       </c>
     </row>
+    <row r="62" spans="1:10" ht="12.75">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="18">
+        <v>1606.4256966586067</v>
+      </c>
+      <c r="F62" s="18">
+        <v>150366.61765662523</v>
+      </c>
+      <c r="G62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="H62" s="18">
+        <v>120000</v>
+      </c>
+      <c r="I62" s="18">
+        <v>187206.43969950231</v>
+      </c>
+      <c r="J62" s="18">
+        <v>67206.439699502313</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>
